--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3925" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3939" uniqueCount="322">
   <si>
     <t>Property</t>
   </si>
@@ -383,6 +383,10 @@
     <t>closed</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -423,6 +427,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -462,6 +476,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -475,24 +492,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -538,9 +562,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Parameters.parameter:rxPrescription.part.id</t>
@@ -1336,7 +1357,7 @@
     <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2093,24 +2114,24 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2133,13 +2154,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2190,7 +2211,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2213,14 +2234,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2239,16 +2260,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2286,19 +2307,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2310,7 +2331,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2321,14 +2342,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2347,19 +2368,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2408,7 +2429,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2420,21 +2441,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2457,15 +2478,17 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2514,7 +2537,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2537,10 +2560,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2563,13 +2586,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2620,7 +2643,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2629,7 +2652,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2638,15 +2661,15 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2669,16 +2692,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2728,7 +2751,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2737,7 +2760,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2746,15 +2769,15 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2780,13 +2803,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2836,7 +2859,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2848,7 +2871,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
@@ -2859,13 +2882,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2890,7 +2913,7 @@
         <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>116</v>
@@ -2953,24 +2976,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2993,13 +3016,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3050,7 +3073,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3073,14 +3096,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3099,16 +3122,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3146,19 +3169,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3170,7 +3193,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -3181,14 +3204,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3207,19 +3230,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3268,7 +3291,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3280,21 +3303,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3317,22 +3340,24 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3374,7 +3399,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3397,10 +3422,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3423,13 +3448,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3480,7 +3505,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3489,7 +3514,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3498,15 +3523,15 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3529,16 +3554,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3588,7 +3613,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3597,7 +3622,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3606,15 +3631,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3622,7 +3647,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
@@ -3640,13 +3665,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3691,10 +3716,10 @@
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3706,7 +3731,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
@@ -3717,10 +3742,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3743,13 +3768,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3800,7 +3825,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3823,14 +3848,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3849,16 +3874,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3896,19 +3921,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3920,7 +3945,7 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
@@ -3931,14 +3956,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3957,19 +3982,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4018,7 +4043,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4030,21 +4055,21 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4067,15 +4092,17 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4124,7 +4151,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -4147,10 +4174,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4173,13 +4200,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4230,7 +4257,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4239,7 +4266,7 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>96</v>
@@ -4248,15 +4275,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4279,16 +4306,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4338,7 +4365,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4347,7 +4374,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>75</v>
@@ -4356,15 +4383,15 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4390,13 +4417,13 @@
         <v>75</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4446,7 +4473,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4458,7 +4485,7 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
@@ -4469,13 +4496,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4500,13 +4527,13 @@
         <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4556,7 +4583,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4568,7 +4595,7 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
@@ -4579,10 +4606,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4605,13 +4632,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4662,7 +4689,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4685,14 +4712,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4711,16 +4738,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4758,19 +4785,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4782,7 +4809,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -4793,14 +4820,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4819,19 +4846,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -4880,7 +4907,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4892,21 +4919,21 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4929,22 +4956,24 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>75</v>
@@ -4986,7 +5015,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -5009,10 +5038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5035,13 +5064,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5092,7 +5121,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5101,7 +5130,7 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>96</v>
@@ -5110,15 +5139,15 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5141,16 +5170,16 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5200,7 +5229,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5209,7 +5238,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>75</v>
@@ -5218,15 +5247,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5252,13 +5281,13 @@
         <v>75</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5308,7 +5337,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5320,7 +5349,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
@@ -5331,13 +5360,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
@@ -5362,13 +5391,13 @@
         <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5418,7 +5447,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5430,7 +5459,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5441,10 +5470,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5467,13 +5496,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5524,7 +5553,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5547,14 +5576,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5573,16 +5602,16 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5620,19 +5649,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5644,7 +5673,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
@@ -5655,14 +5684,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5681,19 +5710,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -5742,7 +5771,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5754,21 +5783,21 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5791,22 +5820,24 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>75</v>
@@ -5848,7 +5879,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -5871,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5897,13 +5928,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5954,7 +5985,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5963,7 +5994,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>96</v>
@@ -5972,15 +6003,15 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6003,16 +6034,16 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6062,7 +6093,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6071,7 +6102,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>75</v>
@@ -6080,15 +6111,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6114,13 +6145,13 @@
         <v>75</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6170,7 +6201,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6182,7 +6213,7 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6193,13 +6224,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>75</v>
@@ -6224,13 +6255,13 @@
         <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6280,7 +6311,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6292,7 +6323,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6303,10 +6334,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6329,13 +6360,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6386,7 +6417,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6409,14 +6440,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6435,16 +6466,16 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6482,19 +6513,19 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6506,7 +6537,7 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6517,14 +6548,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6543,19 +6574,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6604,7 +6635,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6616,21 +6647,21 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6653,22 +6684,24 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>75</v>
@@ -6710,7 +6743,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -6733,10 +6766,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6759,13 +6792,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6816,7 +6849,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -6825,7 +6858,7 @@
         <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>96</v>
@@ -6834,19 +6867,19 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -6865,16 +6898,16 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6924,7 +6957,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6942,15 +6975,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6976,13 +7009,13 @@
         <v>75</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7032,7 +7065,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7044,7 +7077,7 @@
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -7055,13 +7088,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>75</v>
@@ -7086,13 +7119,13 @@
         <v>114</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7142,7 +7175,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7154,7 +7187,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
@@ -7165,10 +7198,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7191,13 +7224,13 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7248,7 +7281,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7271,14 +7304,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7297,16 +7330,16 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7344,19 +7377,19 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7368,7 +7401,7 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -7379,14 +7412,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7405,19 +7438,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7466,7 +7499,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7478,21 +7511,21 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7515,22 +7548,24 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>75</v>
@@ -7572,7 +7607,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -7595,10 +7630,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7621,13 +7656,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7678,7 +7713,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7687,7 +7722,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>96</v>
@@ -7696,15 +7731,15 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7727,16 +7762,16 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7786,7 +7821,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7804,15 +7839,15 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7838,13 +7873,13 @@
         <v>75</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7894,7 +7929,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7906,7 +7941,7 @@
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -7917,13 +7952,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>75</v>
@@ -7948,7 +7983,7 @@
         <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>116</v>
@@ -8011,24 +8046,24 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8051,13 +8086,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8108,7 +8143,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8131,14 +8166,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8157,16 +8192,16 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8204,19 +8239,19 @@
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8228,7 +8263,7 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
@@ -8239,14 +8274,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8265,19 +8300,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8326,7 +8361,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8338,21 +8373,21 @@
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8375,22 +8410,24 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>75</v>
@@ -8432,7 +8469,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -8455,10 +8492,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8481,13 +8518,13 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8538,7 +8575,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8547,7 +8584,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -8556,15 +8593,15 @@
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8587,16 +8624,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8646,7 +8683,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8655,7 +8692,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>75</v>
@@ -8664,15 +8701,15 @@
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8698,13 +8735,13 @@
         <v>78</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8749,10 +8786,10 @@
         <v>75</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -8764,7 +8801,7 @@
         <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
@@ -8775,10 +8812,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8801,13 +8838,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8858,7 +8895,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -8881,14 +8918,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8907,16 +8944,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8954,19 +8991,19 @@
         <v>75</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -8978,7 +9015,7 @@
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -8989,14 +9026,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9015,19 +9052,19 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9076,7 +9113,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9088,21 +9125,21 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9125,15 +9162,17 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9182,7 +9221,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -9205,10 +9244,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9231,13 +9270,13 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9288,7 +9327,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -9297,7 +9336,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -9306,15 +9345,15 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9337,16 +9376,16 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9396,7 +9435,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9405,7 +9444,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>75</v>
@@ -9414,15 +9453,15 @@
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9448,13 +9487,13 @@
         <v>75</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9504,7 +9543,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9516,7 +9555,7 @@
         <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -9527,13 +9566,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -9558,13 +9597,13 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9614,7 +9653,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9626,7 +9665,7 @@
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9637,10 +9676,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9663,13 +9702,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9720,7 +9759,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -9743,14 +9782,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9769,16 +9808,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9816,19 +9855,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -9840,7 +9879,7 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -9851,14 +9890,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -9877,19 +9916,19 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -9938,7 +9977,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -9950,21 +9989,21 @@
         <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9987,22 +10026,24 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -10044,7 +10085,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>84</v>
@@ -10067,10 +10108,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10093,13 +10134,13 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10150,7 +10191,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10159,7 +10200,7 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>96</v>
@@ -10168,15 +10209,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10199,16 +10240,16 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10258,7 +10299,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10267,7 +10308,7 @@
         <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>75</v>
@@ -10276,15 +10317,15 @@
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10310,13 +10351,13 @@
         <v>78</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10361,10 +10402,10 @@
         <v>75</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10376,7 +10417,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10387,10 +10428,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10413,13 +10454,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10470,7 +10511,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10493,14 +10534,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10519,16 +10560,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10566,19 +10607,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10590,7 +10631,7 @@
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
@@ -10601,14 +10642,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10627,19 +10668,19 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -10688,7 +10729,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10700,21 +10741,21 @@
         <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10737,15 +10778,17 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -10794,7 +10837,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -10817,10 +10860,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10843,13 +10886,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10900,7 +10943,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -10909,7 +10952,7 @@
         <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>96</v>
@@ -10918,15 +10961,15 @@
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10949,16 +10992,16 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11008,7 +11051,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11017,7 +11060,7 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
@@ -11026,15 +11069,15 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11060,13 +11103,13 @@
         <v>75</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11116,7 +11159,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11128,7 +11171,7 @@
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
@@ -11139,13 +11182,13 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -11170,13 +11213,13 @@
         <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11226,7 +11269,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11238,7 +11281,7 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -11249,10 +11292,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11275,13 +11318,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11332,7 +11375,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11355,14 +11398,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11381,16 +11424,16 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11428,19 +11471,19 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11452,7 +11495,7 @@
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
@@ -11463,14 +11506,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11489,19 +11532,19 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11550,7 +11593,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -11562,21 +11605,21 @@
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11599,22 +11642,24 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>75</v>
@@ -11656,7 +11701,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -11679,10 +11724,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11705,13 +11750,13 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11762,7 +11807,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -11771,7 +11816,7 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>96</v>
@@ -11780,15 +11825,15 @@
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11811,16 +11856,16 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11870,7 +11915,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -11888,15 +11933,15 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11922,13 +11967,13 @@
         <v>75</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11978,7 +12023,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -11990,7 +12035,7 @@
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -12001,13 +12046,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -12032,13 +12077,13 @@
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12088,7 +12133,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12100,7 +12145,7 @@
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -12111,10 +12156,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12137,13 +12182,13 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12194,7 +12239,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12217,14 +12262,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -12243,16 +12288,16 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12290,19 +12335,19 @@
         <v>75</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -12314,7 +12359,7 @@
         <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -12325,14 +12370,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -12351,19 +12396,19 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12412,7 +12457,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12424,21 +12469,21 @@
         <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12461,22 +12506,24 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>75</v>
@@ -12518,7 +12565,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>84</v>
@@ -12541,10 +12588,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12567,13 +12614,13 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12624,7 +12671,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12633,7 +12680,7 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>96</v>
@@ -12642,15 +12689,15 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12673,16 +12720,16 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12732,7 +12779,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -12750,15 +12797,15 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12784,13 +12831,13 @@
         <v>75</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12840,7 +12887,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -12852,7 +12899,7 @@
         <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -12863,13 +12910,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>75</v>
@@ -12894,13 +12941,13 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12950,7 +12997,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -12962,7 +13009,7 @@
         <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
@@ -12973,10 +13020,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12999,13 +13046,13 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13056,7 +13103,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13079,14 +13126,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -13105,16 +13152,16 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13152,19 +13199,19 @@
         <v>75</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13176,7 +13223,7 @@
         <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -13187,14 +13234,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -13213,19 +13260,19 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13274,7 +13321,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13286,21 +13333,21 @@
         <v>75</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13323,22 +13370,24 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>75</v>
@@ -13380,7 +13429,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>84</v>
@@ -13403,10 +13452,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13429,13 +13478,13 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13486,7 +13535,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13495,7 +13544,7 @@
         <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>96</v>
@@ -13504,15 +13553,15 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13535,16 +13584,16 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13594,7 +13643,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13609,18 +13658,18 @@
         <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13646,13 +13695,13 @@
         <v>75</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13702,7 +13751,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -13714,7 +13763,7 @@
         <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3939" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3925" uniqueCount="316">
   <si>
     <t>Property</t>
   </si>
@@ -383,10 +383,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -427,16 +423,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -476,9 +462,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -492,8 +475,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -512,13 +495,6 @@
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
   </si>
   <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Parameters.parameter.part</t>
   </si>
   <si>
@@ -562,6 +538,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Parameters.parameter:rxPrescription.part.id</t>
@@ -1357,7 +1336,7 @@
     <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2114,24 +2093,24 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2154,13 +2133,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2211,7 +2190,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2234,14 +2213,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2260,16 +2239,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2307,19 +2286,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2331,7 +2310,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2342,14 +2321,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2368,19 +2347,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2429,7 +2408,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2441,21 +2420,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2478,17 +2457,15 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2537,7 +2514,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2560,10 +2537,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2586,13 +2563,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2643,7 +2620,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2652,7 +2629,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2661,15 +2638,15 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2692,16 +2669,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2751,7 +2728,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2760,7 +2737,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2769,15 +2746,15 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2803,13 +2780,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2859,7 +2836,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2871,7 +2848,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
@@ -2882,13 +2859,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2913,7 +2890,7 @@
         <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>116</v>
@@ -2976,24 +2953,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3016,13 +2993,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3073,7 +3050,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3096,14 +3073,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3122,16 +3099,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3169,19 +3146,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3193,7 +3170,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -3204,14 +3181,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3230,19 +3207,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3291,7 +3268,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3303,21 +3280,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3340,24 +3317,22 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3399,7 +3374,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3422,10 +3397,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3448,13 +3423,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3505,7 +3480,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3514,7 +3489,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3523,15 +3498,15 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3554,16 +3529,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3613,7 +3588,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3622,7 +3597,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3631,15 +3606,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3647,7 +3622,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
@@ -3665,13 +3640,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3716,10 +3691,10 @@
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3731,7 +3706,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
@@ -3742,10 +3717,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3768,13 +3743,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3825,7 +3800,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3848,14 +3823,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3874,16 +3849,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3921,19 +3896,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3945,7 +3920,7 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
@@ -3956,14 +3931,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3982,19 +3957,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4043,7 +4018,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4055,21 +4030,21 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4092,17 +4067,15 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4151,7 +4124,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -4174,10 +4147,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4200,13 +4173,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4257,7 +4230,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4266,7 +4239,7 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>96</v>
@@ -4275,15 +4248,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4306,16 +4279,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4365,7 +4338,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4374,7 +4347,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>75</v>
@@ -4383,15 +4356,15 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4417,13 +4390,13 @@
         <v>75</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4473,7 +4446,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4485,7 +4458,7 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
@@ -4496,13 +4469,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4527,13 +4500,13 @@
         <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4583,7 +4556,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4595,7 +4568,7 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
@@ -4606,10 +4579,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4632,13 +4605,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4689,7 +4662,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4712,14 +4685,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4738,16 +4711,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4785,19 +4758,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4809,7 +4782,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -4820,14 +4793,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4846,19 +4819,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -4907,7 +4880,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4919,21 +4892,21 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4956,24 +4929,22 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>75</v>
@@ -5015,7 +4986,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -5038,10 +5009,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5064,13 +5035,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5121,7 +5092,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5130,7 +5101,7 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>96</v>
@@ -5139,15 +5110,15 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5170,16 +5141,16 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5229,7 +5200,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5238,7 +5209,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>75</v>
@@ -5247,15 +5218,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5281,13 +5252,13 @@
         <v>75</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5337,7 +5308,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5349,7 +5320,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
@@ -5360,13 +5331,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
@@ -5391,13 +5362,13 @@
         <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5447,7 +5418,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5459,7 +5430,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5470,10 +5441,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5496,13 +5467,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5553,7 +5524,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5576,14 +5547,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5602,16 +5573,16 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5649,19 +5620,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5673,7 +5644,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
@@ -5684,14 +5655,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5710,19 +5681,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -5771,7 +5742,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5783,21 +5754,21 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5820,24 +5791,22 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>75</v>
@@ -5879,7 +5848,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -5902,10 +5871,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5928,13 +5897,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5985,7 +5954,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5994,7 +5963,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>96</v>
@@ -6003,15 +5972,15 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6034,16 +6003,16 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6093,7 +6062,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6102,7 +6071,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>75</v>
@@ -6111,15 +6080,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6145,13 +6114,13 @@
         <v>75</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6201,7 +6170,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6213,7 +6182,7 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6224,13 +6193,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>75</v>
@@ -6255,13 +6224,13 @@
         <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6311,7 +6280,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6323,7 +6292,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6334,10 +6303,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6360,13 +6329,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6417,7 +6386,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6440,14 +6409,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6466,16 +6435,16 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6513,19 +6482,19 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6537,7 +6506,7 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6548,14 +6517,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6574,19 +6543,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6635,7 +6604,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6647,21 +6616,21 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6684,24 +6653,22 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>75</v>
@@ -6743,7 +6710,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -6766,10 +6733,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6792,13 +6759,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6849,7 +6816,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -6858,7 +6825,7 @@
         <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>96</v>
@@ -6867,19 +6834,19 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -6898,16 +6865,16 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6957,7 +6924,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6975,15 +6942,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7009,13 +6976,13 @@
         <v>75</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7065,7 +7032,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7077,7 +7044,7 @@
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -7088,13 +7055,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>75</v>
@@ -7119,13 +7086,13 @@
         <v>114</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7175,7 +7142,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7187,7 +7154,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
@@ -7198,10 +7165,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7224,13 +7191,13 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7281,7 +7248,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7304,14 +7271,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7330,16 +7297,16 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7377,19 +7344,19 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7401,7 +7368,7 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -7412,14 +7379,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7438,19 +7405,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7499,7 +7466,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7511,21 +7478,21 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7548,24 +7515,22 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>75</v>
@@ -7607,7 +7572,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -7630,10 +7595,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7656,13 +7621,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7713,7 +7678,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7722,7 +7687,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>96</v>
@@ -7731,15 +7696,15 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7762,16 +7727,16 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7821,7 +7786,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7839,15 +7804,15 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7873,13 +7838,13 @@
         <v>75</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7929,7 +7894,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7941,7 +7906,7 @@
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -7952,13 +7917,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>75</v>
@@ -7983,7 +7948,7 @@
         <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>116</v>
@@ -8046,24 +8011,24 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8086,13 +8051,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8143,7 +8108,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8166,14 +8131,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8192,16 +8157,16 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8239,19 +8204,19 @@
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8263,7 +8228,7 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
@@ -8274,14 +8239,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8300,19 +8265,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8361,7 +8326,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8373,21 +8338,21 @@
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8410,24 +8375,22 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>75</v>
@@ -8469,7 +8432,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -8492,10 +8455,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8518,13 +8481,13 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8575,7 +8538,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8584,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -8593,15 +8556,15 @@
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8624,16 +8587,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8683,7 +8646,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8692,7 +8655,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>75</v>
@@ -8701,15 +8664,15 @@
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8735,13 +8698,13 @@
         <v>78</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8786,10 +8749,10 @@
         <v>75</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -8801,7 +8764,7 @@
         <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
@@ -8812,10 +8775,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8838,13 +8801,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8895,7 +8858,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -8918,14 +8881,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8944,16 +8907,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8991,19 +8954,19 @@
         <v>75</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9015,7 +8978,7 @@
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -9026,14 +8989,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9052,19 +9015,19 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9113,7 +9076,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9125,21 +9088,21 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9162,17 +9125,15 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9221,7 +9182,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -9244,10 +9205,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9270,13 +9231,13 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9327,7 +9288,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -9336,7 +9297,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -9345,15 +9306,15 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9376,16 +9337,16 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9435,7 +9396,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9444,7 +9405,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>75</v>
@@ -9453,15 +9414,15 @@
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9487,13 +9448,13 @@
         <v>75</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9543,7 +9504,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9555,7 +9516,7 @@
         <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -9566,13 +9527,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -9597,13 +9558,13 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9653,7 +9614,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9665,7 +9626,7 @@
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9676,10 +9637,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9702,13 +9663,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9759,7 +9720,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -9782,14 +9743,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9808,16 +9769,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9855,19 +9816,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -9879,7 +9840,7 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -9890,14 +9851,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -9916,19 +9877,19 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -9977,7 +9938,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -9989,21 +9950,21 @@
         <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10026,24 +9987,22 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -10085,7 +10044,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>84</v>
@@ -10108,10 +10067,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10134,13 +10093,13 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10191,7 +10150,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10200,7 +10159,7 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>96</v>
@@ -10209,15 +10168,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10240,16 +10199,16 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10299,7 +10258,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10308,7 +10267,7 @@
         <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>75</v>
@@ -10317,15 +10276,15 @@
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10351,13 +10310,13 @@
         <v>78</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10402,10 +10361,10 @@
         <v>75</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10417,7 +10376,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10428,10 +10387,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10454,13 +10413,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10511,7 +10470,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10534,14 +10493,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10560,16 +10519,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10607,19 +10566,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10631,7 +10590,7 @@
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
@@ -10642,14 +10601,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10668,19 +10627,19 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -10729,7 +10688,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10741,21 +10700,21 @@
         <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10778,17 +10737,15 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -10837,7 +10794,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -10860,10 +10817,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10886,13 +10843,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10943,7 +10900,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -10952,7 +10909,7 @@
         <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>96</v>
@@ -10961,15 +10918,15 @@
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10992,16 +10949,16 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11051,7 +11008,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11060,7 +11017,7 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
@@ -11069,15 +11026,15 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11103,13 +11060,13 @@
         <v>75</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11159,7 +11116,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11171,7 +11128,7 @@
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
@@ -11182,13 +11139,13 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -11213,13 +11170,13 @@
         <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11269,7 +11226,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11281,7 +11238,7 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -11292,10 +11249,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11318,13 +11275,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11375,7 +11332,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11398,14 +11355,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11424,16 +11381,16 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11471,19 +11428,19 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11495,7 +11452,7 @@
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
@@ -11506,14 +11463,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11532,19 +11489,19 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11593,7 +11550,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -11605,21 +11562,21 @@
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11642,24 +11599,22 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>75</v>
@@ -11701,7 +11656,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -11724,10 +11679,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11750,13 +11705,13 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11807,7 +11762,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -11816,7 +11771,7 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>96</v>
@@ -11825,15 +11780,15 @@
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11856,16 +11811,16 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11915,7 +11870,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -11933,15 +11888,15 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11967,13 +11922,13 @@
         <v>75</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12023,7 +11978,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12035,7 +11990,7 @@
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -12046,13 +12001,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -12077,13 +12032,13 @@
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12133,7 +12088,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12145,7 +12100,7 @@
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -12156,10 +12111,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12182,13 +12137,13 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12239,7 +12194,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12262,14 +12217,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -12288,16 +12243,16 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12335,19 +12290,19 @@
         <v>75</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -12359,7 +12314,7 @@
         <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -12370,14 +12325,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -12396,19 +12351,19 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12457,7 +12412,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12469,21 +12424,21 @@
         <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12506,24 +12461,22 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>75</v>
@@ -12565,7 +12518,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>84</v>
@@ -12588,10 +12541,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12614,13 +12567,13 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12671,7 +12624,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12680,7 +12633,7 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>96</v>
@@ -12689,15 +12642,15 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12720,16 +12673,16 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12779,7 +12732,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -12797,15 +12750,15 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12831,13 +12784,13 @@
         <v>75</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12887,7 +12840,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -12899,7 +12852,7 @@
         <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -12910,13 +12863,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>75</v>
@@ -12941,13 +12894,13 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12997,7 +12950,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13009,7 +12962,7 @@
         <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
@@ -13020,10 +12973,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13046,13 +12999,13 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13103,7 +13056,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13126,14 +13079,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -13152,16 +13105,16 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13199,19 +13152,19 @@
         <v>75</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13223,7 +13176,7 @@
         <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -13234,14 +13187,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -13260,19 +13213,19 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13321,7 +13274,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13333,21 +13286,21 @@
         <v>75</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13370,24 +13323,22 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>75</v>
@@ -13429,7 +13380,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>84</v>
@@ -13452,10 +13403,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13478,13 +13429,13 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13535,7 +13486,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13544,7 +13495,7 @@
         <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>96</v>
@@ -13553,15 +13504,15 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13584,16 +13535,16 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13643,7 +13594,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13658,18 +13609,18 @@
         <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13695,13 +13646,13 @@
         <v>75</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13751,7 +13702,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -13763,7 +13714,7 @@
         <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
